--- a/public/downloads/YangIntrinsic2016.xlsx
+++ b/public/downloads/YangIntrinsic2016.xlsx
@@ -8,29 +8,31 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="3" r:id="rId3"/>
-    <sheet name="CHGNetv0.3.0" sheetId="4" r:id="rId4"/>
-    <sheet name="DPA-3.1-3M-FT" sheetId="5" r:id="rId5"/>
-    <sheet name="Eqnorm-MPtrj" sheetId="6" r:id="rId6"/>
-    <sheet name="eSEN-30M-OAM" sheetId="7" r:id="rId7"/>
-    <sheet name="GRACE-2L-OAM" sheetId="8" r:id="rId8"/>
-    <sheet name="MACE-MPA-0" sheetId="9" r:id="rId9"/>
-    <sheet name="MATLANTISv8" sheetId="10" r:id="rId10"/>
-    <sheet name="MatterSim_v1_5M" sheetId="11" r:id="rId11"/>
-    <sheet name="ORB-v3" sheetId="12" r:id="rId12"/>
-    <sheet name="SevenNet-MF-OMPA" sheetId="13" r:id="rId13"/>
-    <sheet name="UMA-m-1p1_oc20" sheetId="14" r:id="rId14"/>
-    <sheet name="UMA-m-1p1_omat" sheetId="15" r:id="rId15"/>
-    <sheet name="UMA-s-1p1_oc20" sheetId="16" r:id="rId16"/>
-    <sheet name="UMA-s-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="5" r:id="rId5"/>
+    <sheet name="CHGNetv0.3.0" sheetId="6" r:id="rId6"/>
+    <sheet name="DPA-3.1-3M-FT" sheetId="7" r:id="rId7"/>
+    <sheet name="Eqnorm-MPtrj" sheetId="8" r:id="rId8"/>
+    <sheet name="eSEN-30M-OAM" sheetId="9" r:id="rId9"/>
+    <sheet name="GRACE-2L-OAM" sheetId="10" r:id="rId10"/>
+    <sheet name="MACE-MPA-0" sheetId="11" r:id="rId11"/>
+    <sheet name="MATLANTISv8" sheetId="12" r:id="rId12"/>
+    <sheet name="MatterSim_v1_5M" sheetId="13" r:id="rId13"/>
+    <sheet name="ORB-v3" sheetId="14" r:id="rId14"/>
+    <sheet name="SevenNet-MF-OMPA" sheetId="15" r:id="rId15"/>
+    <sheet name="UMA-m-1p1_oc20" sheetId="16" r:id="rId16"/>
+    <sheet name="UMA-m-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="UMA-s-1p1_oc20" sheetId="18" r:id="rId18"/>
+    <sheet name="UMA-s-1p1_omat" sheetId="19" r:id="rId19"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="57">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -62,10 +64,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -167,19 +169,40 @@
     <t>Adsorbate_name</t>
   </si>
   <si>
-    <t>H</t>
+    <t>Gas shift correction</t>
+  </si>
+  <si>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
+  </si>
+  <si>
+    <t>CH3CH2OH</t>
   </si>
   <si>
     <t>CH3CHO</t>
   </si>
   <si>
-    <t>CH3CH2OH</t>
+    <t>CH4</t>
   </si>
   <si>
     <t>CO</t>
   </si>
   <si>
-    <t>CH4</t>
+    <t>H</t>
   </si>
 </sst>
 </file>
@@ -665,10 +688,10 @@
         <v>10</v>
       </c>
       <c r="N3" s="5">
-        <v>25.18252205848694</v>
+        <v>25182.52205848694</v>
       </c>
       <c r="O3" s="4">
-        <v>0.03357669607798258</v>
+        <v>33.57669607798258</v>
       </c>
       <c r="P3" s="5">
         <v>750</v>
@@ -715,10 +738,10 @@
         <v>10</v>
       </c>
       <c r="N4" s="5">
-        <v>76.89424228668213</v>
+        <v>76894.24228668213</v>
       </c>
       <c r="O4" s="4">
-        <v>0.05310375848527771</v>
+        <v>53.10375848527772</v>
       </c>
       <c r="P4" s="5">
         <v>1448</v>
@@ -765,10 +788,10 @@
         <v>8</v>
       </c>
       <c r="N5" s="5">
-        <v>228.7293345928192</v>
+        <v>228729.3345928192</v>
       </c>
       <c r="O5" s="4">
-        <v>0.405548465590105</v>
+        <v>405.548465590105</v>
       </c>
       <c r="P5" s="5">
         <v>564</v>
@@ -815,10 +838,10 @@
         <v>10</v>
       </c>
       <c r="N6" s="5">
-        <v>105.6371743679047</v>
+        <v>105637.1743679047</v>
       </c>
       <c r="O6" s="4">
-        <v>0.09083162026475035</v>
+        <v>90.83162026475034</v>
       </c>
       <c r="P6" s="5">
         <v>1163</v>
@@ -865,10 +888,10 @@
         <v>10</v>
       </c>
       <c r="N7" s="5">
-        <v>109.4666414260864</v>
+        <v>109466.6414260864</v>
       </c>
       <c r="O7" s="4">
-        <v>0.1636272667056598</v>
+        <v>163.6272667056598</v>
       </c>
       <c r="P7" s="5">
         <v>669</v>
@@ -915,10 +938,10 @@
         <v>10</v>
       </c>
       <c r="N8" s="5">
-        <v>10.76901793479919</v>
+        <v>10769.01793479919</v>
       </c>
       <c r="O8" s="4">
-        <v>0.01295910702141901</v>
+        <v>12.95910702141901</v>
       </c>
       <c r="P8" s="5">
         <v>831</v>
@@ -965,10 +988,10 @@
         <v>10</v>
       </c>
       <c r="N9" s="5">
-        <v>52.81544327735901</v>
+        <v>52815.44327735901</v>
       </c>
       <c r="O9" s="4">
-        <v>0.03134447672246825</v>
+        <v>31.34447672246825</v>
       </c>
       <c r="P9" s="5">
         <v>1685</v>
@@ -1015,10 +1038,10 @@
         <v>10</v>
       </c>
       <c r="N10" s="5">
-        <v>67.83127784729004</v>
+        <v>67831.27784729004</v>
       </c>
       <c r="O10" s="4">
-        <v>0.08936927252607384</v>
+        <v>89.36927252607384</v>
       </c>
       <c r="P10" s="5">
         <v>759</v>
@@ -1065,10 +1088,10 @@
         <v>10</v>
       </c>
       <c r="N11" s="5">
-        <v>53.33916974067688</v>
+        <v>53339.16974067688</v>
       </c>
       <c r="O11" s="4">
-        <v>0.04173643954669552</v>
+        <v>41.73643954669552</v>
       </c>
       <c r="P11" s="5">
         <v>1278</v>
@@ -1115,10 +1138,10 @@
         <v>10</v>
       </c>
       <c r="N12" s="5">
-        <v>17.31477618217468</v>
+        <v>17314.77618217468</v>
       </c>
       <c r="O12" s="4">
-        <v>0.02027491356226544</v>
+        <v>20.27491356226544</v>
       </c>
       <c r="P12" s="5">
         <v>854</v>
@@ -1165,10 +1188,10 @@
         <v>10</v>
       </c>
       <c r="N13" s="5">
-        <v>71.08380532264709</v>
+        <v>71083.80532264709</v>
       </c>
       <c r="O13" s="4">
-        <v>0.08114589648704006</v>
+        <v>81.14589648704006</v>
       </c>
       <c r="P13" s="5">
         <v>876</v>
@@ -1215,10 +1238,10 @@
         <v>10</v>
       </c>
       <c r="N14" s="5">
-        <v>120.5068476200104</v>
+        <v>120506.8476200104</v>
       </c>
       <c r="O14" s="4">
-        <v>0.2148072150089312</v>
+        <v>214.8072150089312</v>
       </c>
       <c r="P14" s="5">
         <v>561</v>
@@ -1265,10 +1288,10 @@
         <v>10</v>
       </c>
       <c r="N15" s="5">
-        <v>184.7918872833252</v>
+        <v>184791.8872833252</v>
       </c>
       <c r="O15" s="4">
-        <v>0.2184301268124411</v>
+        <v>218.4301268124411</v>
       </c>
       <c r="P15" s="5">
         <v>846</v>
@@ -1315,10 +1338,10 @@
         <v>10</v>
       </c>
       <c r="N16" s="5">
-        <v>58.46917724609375</v>
+        <v>58469.17724609375</v>
       </c>
       <c r="O16" s="4">
-        <v>0.1025775039405153</v>
+        <v>102.5775039405153</v>
       </c>
       <c r="P16" s="5">
         <v>570</v>
@@ -1365,10 +1388,10 @@
         <v>10</v>
       </c>
       <c r="N17" s="5">
-        <v>73.83526062965393</v>
+        <v>73835.26062965393</v>
       </c>
       <c r="O17" s="4">
-        <v>0.1000477786309674</v>
+        <v>100.0477786309674</v>
       </c>
       <c r="P17" s="5">
         <v>738</v>
@@ -1396,7 +1419,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1407,9 +1430,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1443,8 +1472,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1466,34 +1503,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2713288744407704</v>
+        <v>0.0989705466116288</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2713288744407704</v>
+        <v>0.04665848753970803</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2588322516570342</v>
+        <v>0.06890249147884159</v>
       </c>
       <c r="E3" s="4">
-        <v>84.08163265306122</v>
+        <v>87.95918367346938</v>
       </c>
       <c r="F3" s="4">
-        <v>91.31991051454138</v>
+        <v>82.34899328859061</v>
       </c>
       <c r="G3" s="5">
         <v>2</v>
       </c>
       <c r="H3" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="5">
         <v>0</v>
@@ -1507,25 +1562,41 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.0989705466116288</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.04665848753970803</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.09944088966121065</v>
+        <v>0.5063011415515828</v>
       </c>
       <c r="C4" s="4">
-        <v>0.09944088966121065</v>
+        <v>0.5063011415515828</v>
       </c>
       <c r="D4" s="4">
-        <v>0.06856443236553453</v>
+        <v>0.4336391435909601</v>
       </c>
       <c r="E4" s="4">
-        <v>85.56122448979592</v>
+        <v>88.5204081632653</v>
       </c>
       <c r="F4" s="4">
-        <v>91.02348993288591</v>
+        <v>82.78523489932886</v>
       </c>
       <c r="G4" s="5">
         <v>2</v>
@@ -1548,25 +1619,41 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>2</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.5063011415515828</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.5063011415515828</v>
+      </c>
+      <c r="R4" s="5">
+        <v>2</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.1218401355144061</v>
+        <v>0.203305479063321</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1218401355144061</v>
+        <v>0.203305479063321</v>
       </c>
       <c r="D5" s="4">
-        <v>0.1890802305603239</v>
+        <v>0.1661119959117807</v>
       </c>
       <c r="E5" s="4">
-        <v>81.88775510204081</v>
+        <v>92.70408163265306</v>
       </c>
       <c r="F5" s="4">
-        <v>85.88926174496645</v>
+        <v>89.66442953020135</v>
       </c>
       <c r="G5" s="5">
         <v>2</v>
@@ -1589,25 +1676,41 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.203305479063321</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.203305479063321</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.2046228117231758</v>
+        <v>0.5791185515845066</v>
       </c>
       <c r="C6" s="4">
-        <v>0.2046228117231758</v>
+        <v>0.5791185515845066</v>
       </c>
       <c r="D6" s="4">
-        <v>0.1997498793203641</v>
+        <v>0.5680738591443836</v>
       </c>
       <c r="E6" s="4">
-        <v>84.08163265306122</v>
+        <v>93.21428571428571</v>
       </c>
       <c r="F6" s="4">
-        <v>92.06375838926175</v>
+        <v>95.85570469798658</v>
       </c>
       <c r="G6" s="5">
         <v>2</v>
@@ -1630,25 +1733,41 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>2</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.5791185515845066</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.5791185515845066</v>
+      </c>
+      <c r="R6" s="5">
+        <v>2</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B7" s="4">
-        <v>0.07215804451875468</v>
+        <v>0.1901778159201312</v>
       </c>
       <c r="C7" s="4">
-        <v>0.07215804451875468</v>
+        <v>0.1901778159201312</v>
       </c>
       <c r="D7" s="4">
-        <v>0.1009750270806469</v>
+        <v>0.1927947598954431</v>
       </c>
       <c r="E7" s="4">
-        <v>88.9795918367347</v>
+        <v>93.82653061224489</v>
       </c>
       <c r="F7" s="4">
-        <v>93.38926174496645</v>
+        <v>96.30872483221476</v>
       </c>
       <c r="G7" s="5">
         <v>2</v>
@@ -1671,9 +1790,25 @@
       <c r="M7" s="5">
         <v>0</v>
       </c>
+      <c r="N7" s="4"/>
+      <c r="O7" s="5">
+        <v>2</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.1901778159201312</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.1901778159201312</v>
+      </c>
+      <c r="R7" s="5">
+        <v>2</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1684,6 +1819,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1691,7 +1827,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1702,9 +1838,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1738,8 +1880,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1761,34 +1911,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4816690769584765</v>
+        <v>0.7018941578789843</v>
       </c>
       <c r="C3" s="4">
-        <v>0.4816690769584765</v>
+        <v>0.8112256956957031</v>
       </c>
       <c r="D3" s="4">
-        <v>0.4642418709190478</v>
+        <v>0.8906415638848437</v>
       </c>
       <c r="E3" s="4">
-        <v>90.30612244897959</v>
+        <v>68.46938775510205</v>
       </c>
       <c r="F3" s="4">
-        <v>95.13422818791946</v>
+        <v>68.47315436241611</v>
       </c>
       <c r="G3" s="5">
         <v>2</v>
       </c>
       <c r="H3" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="5">
         <v>0</v>
@@ -1802,25 +1970,41 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.7018941578789843</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.8112256956957031</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3557717602015</v>
+        <v>0.2162878711461562</v>
       </c>
       <c r="C4" s="4">
-        <v>0.4143220812547188</v>
+        <v>0.2285078137648125</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2439980139243125</v>
+        <v>0.5200903613805312</v>
       </c>
       <c r="E4" s="4">
-        <v>81.37755102040816</v>
+        <v>70.56122448979592</v>
       </c>
       <c r="F4" s="4">
-        <v>72.01342281879195</v>
+        <v>65.1062639821029</v>
       </c>
       <c r="G4" s="5">
         <v>2</v>
@@ -1843,25 +2027,39 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2162878711461562</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2285078137648125</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.3030954661444531</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0</v>
-      </c>
+        <v>0.1709283115775938</v>
+      </c>
+      <c r="C5" s="4"/>
       <c r="D5" s="4">
-        <v>0.09240973616398435</v>
+        <v>0.2939770939262266</v>
       </c>
       <c r="E5" s="4">
-        <v>73.078231292517</v>
+        <v>66.68367346938776</v>
       </c>
       <c r="F5" s="4">
-        <v>64.87695749440715</v>
+        <v>55.12863534675616</v>
       </c>
       <c r="G5" s="5">
         <v>2</v>
@@ -1884,25 +2082,39 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>0</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1709283115775938</v>
+      </c>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="5">
+        <v>0</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.1736591356035938</v>
+        <v>0.2885807772574219</v>
       </c>
       <c r="C6" s="4">
-        <v>0.1736591356035938</v>
+        <v>0.2885807772574219</v>
       </c>
       <c r="D6" s="4">
-        <v>0.1767604844805469</v>
+        <v>0.3125265856680665</v>
       </c>
       <c r="E6" s="4">
-        <v>90.20408163265306</v>
+        <v>79.64285714285714</v>
       </c>
       <c r="F6" s="4">
-        <v>95.45302013422818</v>
+        <v>87.85234899328859</v>
       </c>
       <c r="G6" s="5">
         <v>2</v>
@@ -1925,34 +2137,50 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>2</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.2885807772574219</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.2885807772574219</v>
+      </c>
+      <c r="R6" s="5">
+        <v>2</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B7" s="4">
-        <v>0.2096449611274844</v>
+        <v>0.1790675011070361</v>
       </c>
       <c r="C7" s="4">
-        <v>0.2299542408586406</v>
+        <v>0.1790675011070361</v>
       </c>
       <c r="D7" s="4">
-        <v>0.07747633295381251</v>
+        <v>0.1656404819877734</v>
       </c>
       <c r="E7" s="4">
-        <v>79.74489795918367</v>
+        <v>79.03061224489795</v>
       </c>
       <c r="F7" s="4">
-        <v>72.76845637583892</v>
+        <v>86.19127516778524</v>
       </c>
       <c r="G7" s="5">
         <v>2</v>
       </c>
       <c r="H7" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I7" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" s="5">
         <v>0</v>
@@ -1966,9 +2194,25 @@
       <c r="M7" s="5">
         <v>0</v>
       </c>
+      <c r="N7" s="4"/>
+      <c r="O7" s="5">
+        <v>2</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.1790675011070361</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.1790675011070361</v>
+      </c>
+      <c r="R7" s="5">
+        <v>2</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1979,6 +2223,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1986,7 +2231,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1997,9 +2242,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2033,8 +2284,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2056,25 +2315,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.216610797921001</v>
+        <v>0.1218401355144061</v>
       </c>
       <c r="C3" s="4">
-        <v>0.216610797921001</v>
+        <v>0.1218401355144061</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2087489452751269</v>
+        <v>0.1890802305603239</v>
       </c>
       <c r="E3" s="4">
-        <v>88.65646258503401</v>
+        <v>81.88775510204081</v>
       </c>
       <c r="F3" s="4">
-        <v>91.78970917225951</v>
+        <v>85.88926174496645</v>
       </c>
       <c r="G3" s="5">
         <v>2</v>
@@ -2097,25 +2374,41 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1218401355144061</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1218401355144061</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3621384899378282</v>
+        <v>0.09944088966121065</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3621384899378282</v>
+        <v>0.09944088966121065</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3187882702112657</v>
+        <v>0.06856443236553453</v>
       </c>
       <c r="E4" s="4">
-        <v>89.93197278911565</v>
+        <v>85.56122448979592</v>
       </c>
       <c r="F4" s="4">
-        <v>91.20805369127517</v>
+        <v>91.02348993288591</v>
       </c>
       <c r="G4" s="5">
         <v>2</v>
@@ -2138,25 +2431,41 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>2</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.09944088966121065</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.09944088966121065</v>
+      </c>
+      <c r="R4" s="5">
+        <v>2</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.06566298628605466</v>
+        <v>0.07215804451875468</v>
       </c>
       <c r="C5" s="4">
-        <v>0.06566298628605466</v>
+        <v>0.07215804451875468</v>
       </c>
       <c r="D5" s="4">
-        <v>0.05616991672296873</v>
+        <v>0.1009750270806469</v>
       </c>
       <c r="E5" s="4">
-        <v>84.59183673469387</v>
+        <v>88.9795918367347</v>
       </c>
       <c r="F5" s="4">
-        <v>84.85458612975391</v>
+        <v>93.38926174496645</v>
       </c>
       <c r="G5" s="5">
         <v>2</v>
@@ -2179,25 +2488,41 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.07215804451875468</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.07215804451875468</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.3334540148672852</v>
+        <v>0.2046228117231758</v>
       </c>
       <c r="C6" s="4">
-        <v>0.3334540148672852</v>
+        <v>0.2046228117231758</v>
       </c>
       <c r="D6" s="4">
-        <v>0.3433378954825196</v>
+        <v>0.1997498793203641</v>
       </c>
       <c r="E6" s="4">
-        <v>88.72448979591837</v>
+        <v>84.08163265306122</v>
       </c>
       <c r="F6" s="4">
-        <v>92.3042505592841</v>
+        <v>92.06375838926175</v>
       </c>
       <c r="G6" s="5">
         <v>2</v>
@@ -2220,25 +2545,41 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>2</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.2046228117231758</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.2046228117231758</v>
+      </c>
+      <c r="R6" s="5">
+        <v>2</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B7" s="4">
-        <v>0.02729098773881249</v>
+        <v>0.2713288744407704</v>
       </c>
       <c r="C7" s="4">
-        <v>0.02729098773881249</v>
+        <v>0.2713288744407704</v>
       </c>
       <c r="D7" s="4">
-        <v>0.02872149921342187</v>
+        <v>0.2588322516570342</v>
       </c>
       <c r="E7" s="4">
-        <v>94.0986394557823</v>
+        <v>84.08163265306122</v>
       </c>
       <c r="F7" s="4">
-        <v>94.47986577181209</v>
+        <v>91.31991051454138</v>
       </c>
       <c r="G7" s="5">
         <v>2</v>
@@ -2261,9 +2602,25 @@
       <c r="M7" s="5">
         <v>0</v>
       </c>
+      <c r="N7" s="4"/>
+      <c r="O7" s="5">
+        <v>2</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.2713288744407704</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.2713288744407704</v>
+      </c>
+      <c r="R7" s="5">
+        <v>2</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2274,6 +2631,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2281,7 +2639,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2292,9 +2650,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2328,8 +2692,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2351,34 +2723,50 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.416660675087749</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.416660675087749</v>
-      </c>
+        <v>0.3030954661444531</v>
+      </c>
+      <c r="C3" s="4"/>
       <c r="D3" s="4">
-        <v>0.4104708519371142</v>
+        <v>0.09240973616398435</v>
       </c>
       <c r="E3" s="4">
-        <v>93.21428571428571</v>
+        <v>73.078231292517</v>
       </c>
       <c r="F3" s="4">
-        <v>96.2248322147651</v>
+        <v>64.87695749440715</v>
       </c>
       <c r="G3" s="5">
         <v>2</v>
       </c>
       <c r="H3" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3" s="5">
         <v>0</v>
@@ -2392,34 +2780,48 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3030954661444531</v>
+      </c>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="5">
+        <v>0</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.5878369610071641</v>
+        <v>0.3557717602015</v>
       </c>
       <c r="C4" s="4">
-        <v>0.5878369610071641</v>
+        <v>0.4143220812547188</v>
       </c>
       <c r="D4" s="4">
-        <v>0.5247590343714219</v>
+        <v>0.2439980139243125</v>
       </c>
       <c r="E4" s="4">
-        <v>93.72448979591837</v>
+        <v>81.37755102040816</v>
       </c>
       <c r="F4" s="4">
-        <v>94.26174496644295</v>
+        <v>72.01342281879195</v>
       </c>
       <c r="G4" s="5">
         <v>2</v>
       </c>
       <c r="H4" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="5">
         <v>0</v>
@@ -2433,34 +2835,50 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3557717602015</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.4143220812547188</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.326086646564375</v>
+        <v>0.2096449611274844</v>
       </c>
       <c r="C5" s="4">
-        <v>0.326086646564375</v>
+        <v>0.2299542408586406</v>
       </c>
       <c r="D5" s="4">
-        <v>0.21350730086125</v>
+        <v>0.07747633295381251</v>
       </c>
       <c r="E5" s="4">
-        <v>85.96938775510205</v>
+        <v>79.74489795918367</v>
       </c>
       <c r="F5" s="4">
-        <v>82.83557046979865</v>
+        <v>72.76845637583892</v>
       </c>
       <c r="G5" s="5">
         <v>2</v>
       </c>
       <c r="H5" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="5">
         <v>0</v>
@@ -2474,25 +2892,41 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2096449611274844</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2299542408586406</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.6783522387442383</v>
+        <v>0.1736591356035938</v>
       </c>
       <c r="C6" s="4">
-        <v>0.6783522387442383</v>
+        <v>0.1736591356035938</v>
       </c>
       <c r="D6" s="4">
-        <v>0.6409882327017579</v>
+        <v>0.1767604844805469</v>
       </c>
       <c r="E6" s="4">
-        <v>92.5</v>
+        <v>90.20408163265306</v>
       </c>
       <c r="F6" s="4">
-        <v>95.41946308724832</v>
+        <v>95.45302013422818</v>
       </c>
       <c r="G6" s="5">
         <v>2</v>
@@ -2515,34 +2949,50 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>2</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.1736591356035938</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.1736591356035938</v>
+      </c>
+      <c r="R6" s="5">
+        <v>2</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B7" s="4">
-        <v>0.4861876247017031</v>
+        <v>0.4816690769584765</v>
       </c>
       <c r="C7" s="4">
-        <v>0.4479492678221094</v>
+        <v>0.4816690769584765</v>
       </c>
       <c r="D7" s="4">
-        <v>0.4053084132759219</v>
+        <v>0.4642418709190478</v>
       </c>
       <c r="E7" s="4">
-        <v>83.01020408163265</v>
+        <v>90.30612244897959</v>
       </c>
       <c r="F7" s="4">
-        <v>70.28523489932886</v>
+        <v>95.13422818791946</v>
       </c>
       <c r="G7" s="5">
         <v>2</v>
       </c>
       <c r="H7" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I7" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" s="5">
         <v>0</v>
@@ -2556,9 +3006,25 @@
       <c r="M7" s="5">
         <v>0</v>
       </c>
+      <c r="N7" s="4"/>
+      <c r="O7" s="5">
+        <v>2</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.4816690769584765</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.4816690769584765</v>
+      </c>
+      <c r="R7" s="5">
+        <v>2</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2569,6 +3035,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2576,7 +3043,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2587,9 +3054,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2623,8 +3096,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2646,25 +3127,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.06319625047761107</v>
+        <v>0.06566298628605466</v>
       </c>
       <c r="C3" s="4">
-        <v>0.06319625047761107</v>
+        <v>0.06566298628605466</v>
       </c>
       <c r="D3" s="4">
-        <v>0.07191614178734923</v>
+        <v>0.05616991672296873</v>
       </c>
       <c r="E3" s="4">
-        <v>87.75510204081633</v>
+        <v>84.59183673469387</v>
       </c>
       <c r="F3" s="4">
-        <v>94.39597315436242</v>
+        <v>84.85458612975391</v>
       </c>
       <c r="G3" s="5">
         <v>2</v>
@@ -2687,25 +3186,41 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.06566298628605466</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.06566298628605466</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2439332206487908</v>
+        <v>0.3621384899378282</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2439332206487908</v>
+        <v>0.3621384899378282</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2436936099768221</v>
+        <v>0.3187882702112657</v>
       </c>
       <c r="E4" s="4">
-        <v>92.65306122448979</v>
+        <v>89.93197278911565</v>
       </c>
       <c r="F4" s="4">
-        <v>95.70469798657719</v>
+        <v>91.20805369127517</v>
       </c>
       <c r="G4" s="5">
         <v>2</v>
@@ -2728,25 +3243,41 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>2</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3621384899378282</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.3621384899378282</v>
+      </c>
+      <c r="R4" s="5">
+        <v>2</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.3954161343500169</v>
+        <v>0.02729098773881249</v>
       </c>
       <c r="C5" s="4">
-        <v>0.3954161343500169</v>
+        <v>0.02729098773881249</v>
       </c>
       <c r="D5" s="4">
-        <v>0.4088700947687465</v>
+        <v>0.02872149921342187</v>
       </c>
       <c r="E5" s="4">
-        <v>93.36734693877551</v>
+        <v>94.0986394557823</v>
       </c>
       <c r="F5" s="4">
-        <v>95.88926174496645</v>
+        <v>94.47986577181209</v>
       </c>
       <c r="G5" s="5">
         <v>2</v>
@@ -2769,25 +3300,41 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.02729098773881249</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.02729098773881249</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.01458769013850592</v>
+        <v>0.3334540148672852</v>
       </c>
       <c r="C6" s="4">
-        <v>0.01458769013850592</v>
+        <v>0.3334540148672852</v>
       </c>
       <c r="D6" s="4">
-        <v>0.02402293881748052</v>
+        <v>0.3433378954825196</v>
       </c>
       <c r="E6" s="4">
-        <v>87.95918367346938</v>
+        <v>88.72448979591837</v>
       </c>
       <c r="F6" s="4">
-        <v>94.54697986577182</v>
+        <v>92.3042505592841</v>
       </c>
       <c r="G6" s="5">
         <v>2</v>
@@ -2810,25 +3357,41 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>2</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.3334540148672852</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.3334540148672852</v>
+      </c>
+      <c r="R6" s="5">
+        <v>2</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B7" s="4">
-        <v>0.1604369404228086</v>
+        <v>0.216610797921001</v>
       </c>
       <c r="C7" s="4">
-        <v>0.1604369404228086</v>
+        <v>0.216610797921001</v>
       </c>
       <c r="D7" s="4">
-        <v>0.1838896992118711</v>
+        <v>0.2087489452751269</v>
       </c>
       <c r="E7" s="4">
-        <v>93.01020408163265</v>
+        <v>88.65646258503401</v>
       </c>
       <c r="F7" s="4">
-        <v>95.85570469798658</v>
+        <v>91.78970917225951</v>
       </c>
       <c r="G7" s="5">
         <v>2</v>
@@ -2851,9 +3414,25 @@
       <c r="M7" s="5">
         <v>0</v>
       </c>
+      <c r="N7" s="4"/>
+      <c r="O7" s="5">
+        <v>2</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.216610797921001</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.216610797921001</v>
+      </c>
+      <c r="R7" s="5">
+        <v>2</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2864,6 +3443,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2871,7 +3451,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2882,9 +3462,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2918,8 +3504,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2941,25 +3535,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4303231921585335</v>
+        <v>0.326086646564375</v>
       </c>
       <c r="C3" s="4">
-        <v>0.4303231921585335</v>
+        <v>0.326086646564375</v>
       </c>
       <c r="D3" s="4">
-        <v>0.4315500345619454</v>
+        <v>0.21350730086125</v>
       </c>
       <c r="E3" s="4">
-        <v>84.81292517006803</v>
+        <v>85.96938775510205</v>
       </c>
       <c r="F3" s="4">
-        <v>91.3255033557047</v>
+        <v>82.83557046979865</v>
       </c>
       <c r="G3" s="5">
         <v>2</v>
@@ -2982,25 +3594,41 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.326086646564375</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.326086646564375</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.8704001705409123</v>
+        <v>0.5878369610071641</v>
       </c>
       <c r="C4" s="4">
-        <v>0.8704001705409123</v>
+        <v>0.5878369610071641</v>
       </c>
       <c r="D4" s="4">
-        <v>0.8296894829035264</v>
+        <v>0.5247590343714219</v>
       </c>
       <c r="E4" s="4">
-        <v>86.73469387755102</v>
+        <v>93.72448979591837</v>
       </c>
       <c r="F4" s="4">
-        <v>90.85570469798658</v>
+        <v>94.26174496644295</v>
       </c>
       <c r="G4" s="5">
         <v>2</v>
@@ -3023,34 +3651,50 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>2</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.5878369610071641</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.5878369610071641</v>
+      </c>
+      <c r="R4" s="5">
+        <v>2</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.4690316977576975</v>
+        <v>0.4861876247017031</v>
       </c>
       <c r="C5" s="4">
-        <v>0.4690316977576975</v>
+        <v>0.4479492678221094</v>
       </c>
       <c r="D5" s="4">
-        <v>0.3890894713477854</v>
+        <v>0.4053084132759219</v>
       </c>
       <c r="E5" s="4">
-        <v>81.32653061224489</v>
+        <v>83.01020408163265</v>
       </c>
       <c r="F5" s="4">
-        <v>83.63534675615213</v>
+        <v>70.28523489932886</v>
       </c>
       <c r="G5" s="5">
         <v>2</v>
       </c>
       <c r="H5" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="5">
         <v>0</v>
@@ -3064,25 +3708,41 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.4861876247017031</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.4479492678221094</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.6554142629203662</v>
+        <v>0.6783522387442383</v>
       </c>
       <c r="C6" s="4">
-        <v>0.6554142629203662</v>
+        <v>0.6783522387442383</v>
       </c>
       <c r="D6" s="4">
-        <v>0.6534319241938457</v>
+        <v>0.6409882327017579</v>
       </c>
       <c r="E6" s="4">
-        <v>85.10204081632654</v>
+        <v>92.5</v>
       </c>
       <c r="F6" s="4">
-        <v>92.23154362416108</v>
+        <v>95.41946308724832</v>
       </c>
       <c r="G6" s="5">
         <v>2</v>
@@ -3105,25 +3765,41 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>2</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.6783522387442383</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.6783522387442383</v>
+      </c>
+      <c r="R6" s="5">
+        <v>2</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B7" s="4">
-        <v>0.1698135612099387</v>
+        <v>0.416660675087749</v>
       </c>
       <c r="C7" s="4">
-        <v>0.1698135612099387</v>
+        <v>0.416660675087749</v>
       </c>
       <c r="D7" s="4">
-        <v>0.1490513560859805</v>
+        <v>0.4104708519371142</v>
       </c>
       <c r="E7" s="4">
-        <v>90.86734693877551</v>
+        <v>93.21428571428571</v>
       </c>
       <c r="F7" s="4">
-        <v>93.75838926174497</v>
+        <v>96.2248322147651</v>
       </c>
       <c r="G7" s="5">
         <v>2</v>
@@ -3146,9 +3822,25 @@
       <c r="M7" s="5">
         <v>0</v>
       </c>
+      <c r="N7" s="4"/>
+      <c r="O7" s="5">
+        <v>2</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.416660675087749</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.416660675087749</v>
+      </c>
+      <c r="R7" s="5">
+        <v>2</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3159,6 +3851,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3166,7 +3859,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3177,9 +3870,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3213,8 +3912,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3236,25 +3943,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.06891427306252623</v>
+        <v>0.3954161343500169</v>
       </c>
       <c r="C3" s="4">
-        <v>0.06891427306252623</v>
+        <v>0.3954161343500169</v>
       </c>
       <c r="D3" s="4">
-        <v>0.07145717112141753</v>
+        <v>0.4088700947687465</v>
       </c>
       <c r="E3" s="4">
-        <v>88.36734693877551</v>
+        <v>93.36734693877551</v>
       </c>
       <c r="F3" s="4">
-        <v>94.37919463087249</v>
+        <v>95.88926174496645</v>
       </c>
       <c r="G3" s="5">
         <v>2</v>
@@ -3277,25 +4002,41 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3954161343500169</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3954161343500169</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2617371280431999</v>
+        <v>0.2439332206487908</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2617371280431999</v>
+        <v>0.2439332206487908</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2591037948370232</v>
+        <v>0.2436936099768221</v>
       </c>
       <c r="E4" s="4">
-        <v>92.85714285714286</v>
+        <v>92.65306122448979</v>
       </c>
       <c r="F4" s="4">
-        <v>95.48657718120805</v>
+        <v>95.70469798657719</v>
       </c>
       <c r="G4" s="5">
         <v>2</v>
@@ -3318,22 +4059,38 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>2</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2439332206487908</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2439332206487908</v>
+      </c>
+      <c r="R4" s="5">
+        <v>2</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.4022496876642259</v>
+        <v>0.1604369404228086</v>
       </c>
       <c r="C5" s="4">
-        <v>0.4022496876642259</v>
+        <v>0.1604369404228086</v>
       </c>
       <c r="D5" s="4">
-        <v>0.4119442639276537</v>
+        <v>0.1838896992118711</v>
       </c>
       <c r="E5" s="4">
-        <v>93.77551020408163</v>
+        <v>93.01020408163265</v>
       </c>
       <c r="F5" s="4">
         <v>95.85570469798658</v>
@@ -3359,25 +4116,41 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1604369404228086</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1604369404228086</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.03290313681934209</v>
+        <v>0.01458769013850592</v>
       </c>
       <c r="C6" s="4">
-        <v>0.03290313681934209</v>
+        <v>0.01458769013850592</v>
       </c>
       <c r="D6" s="4">
-        <v>0.04563987454746099</v>
+        <v>0.02402293881748052</v>
       </c>
       <c r="E6" s="4">
-        <v>88.46938775510205</v>
+        <v>87.95918367346938</v>
       </c>
       <c r="F6" s="4">
-        <v>94.68120805369128</v>
+        <v>94.54697986577182</v>
       </c>
       <c r="G6" s="5">
         <v>2</v>
@@ -3400,25 +4173,41 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>2</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.01458769013850592</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.01458769013850592</v>
+      </c>
+      <c r="R6" s="5">
+        <v>2</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B7" s="4">
-        <v>0.1509946110160987</v>
+        <v>0.06319625047761107</v>
       </c>
       <c r="C7" s="4">
-        <v>0.1509946110160987</v>
+        <v>0.06319625047761107</v>
       </c>
       <c r="D7" s="4">
-        <v>0.1737404587181535</v>
+        <v>0.07191614178734923</v>
       </c>
       <c r="E7" s="4">
-        <v>93.5204081632653</v>
+        <v>87.75510204081633</v>
       </c>
       <c r="F7" s="4">
-        <v>95.85570469798658</v>
+        <v>94.39597315436242</v>
       </c>
       <c r="G7" s="5">
         <v>2</v>
@@ -3441,9 +4230,25 @@
       <c r="M7" s="5">
         <v>0</v>
       </c>
+      <c r="N7" s="4"/>
+      <c r="O7" s="5">
+        <v>2</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.06319625047761107</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.06319625047761107</v>
+      </c>
+      <c r="R7" s="5">
+        <v>2</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3454,6 +4259,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3461,7 +4267,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3472,9 +4278,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3508,8 +4320,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3531,25 +4351,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3168147292526213</v>
+        <v>0.4690316977576975</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3168147292526213</v>
+        <v>0.4690316977576975</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3119072702320351</v>
+        <v>0.3890894713477854</v>
       </c>
       <c r="E3" s="4">
-        <v>85.30612244897959</v>
+        <v>81.32653061224489</v>
       </c>
       <c r="F3" s="4">
-        <v>91.61073825503355</v>
+        <v>83.63534675615213</v>
       </c>
       <c r="G3" s="5">
         <v>2</v>
@@ -3572,25 +4410,41 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4690316977576975</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.4690316977576975</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.7680056293248103</v>
+        <v>0.8704001705409123</v>
       </c>
       <c r="C4" s="4">
-        <v>0.7680056293248103</v>
+        <v>0.8704001705409123</v>
       </c>
       <c r="D4" s="4">
-        <v>0.8284495074986384</v>
+        <v>0.8296894829035264</v>
       </c>
       <c r="E4" s="4">
-        <v>87.39795918367346</v>
+        <v>86.73469387755102</v>
       </c>
       <c r="F4" s="4">
-        <v>90.50335570469798</v>
+        <v>90.85570469798658</v>
       </c>
       <c r="G4" s="5">
         <v>2</v>
@@ -3613,25 +4467,41 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>2</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.8704001705409123</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.8704001705409123</v>
+      </c>
+      <c r="R4" s="5">
+        <v>2</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>1.297270172588372</v>
+        <v>0.1698135612099387</v>
       </c>
       <c r="C5" s="4">
-        <v>1.297270172588372</v>
+        <v>0.1698135612099387</v>
       </c>
       <c r="D5" s="4">
-        <v>1.375840300075554</v>
+        <v>0.1490513560859805</v>
       </c>
       <c r="E5" s="4">
-        <v>84.74489795918367</v>
+        <v>90.86734693877551</v>
       </c>
       <c r="F5" s="4">
-        <v>86.34228187919463</v>
+        <v>93.75838926174497</v>
       </c>
       <c r="G5" s="5">
         <v>2</v>
@@ -3654,25 +4524,41 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1698135612099387</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1698135612099387</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.6209464987215861</v>
+        <v>0.6554142629203662</v>
       </c>
       <c r="C6" s="4">
-        <v>0.6209464987215861</v>
+        <v>0.6554142629203662</v>
       </c>
       <c r="D6" s="4">
-        <v>0.5764665623602733</v>
+        <v>0.6534319241938457</v>
       </c>
       <c r="E6" s="4">
-        <v>84.84693877551021</v>
+        <v>85.10204081632654</v>
       </c>
       <c r="F6" s="4">
-        <v>91.77852348993288</v>
+        <v>92.23154362416108</v>
       </c>
       <c r="G6" s="5">
         <v>2</v>
@@ -3695,25 +4581,41 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>2</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.6554142629203662</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.6554142629203662</v>
+      </c>
+      <c r="R6" s="5">
+        <v>2</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B7" s="4">
-        <v>0.7590718986899069</v>
+        <v>0.4303231921585335</v>
       </c>
       <c r="C7" s="4">
-        <v>0.7590718986899069</v>
+        <v>0.4303231921585335</v>
       </c>
       <c r="D7" s="4">
-        <v>0.8197849514395407</v>
+        <v>0.4315500345619454</v>
       </c>
       <c r="E7" s="4">
-        <v>90.66326530612245</v>
+        <v>84.81292517006803</v>
       </c>
       <c r="F7" s="4">
-        <v>93.57382550335571</v>
+        <v>91.3255033557047</v>
       </c>
       <c r="G7" s="5">
         <v>2</v>
@@ -3736,9 +4638,25 @@
       <c r="M7" s="5">
         <v>0</v>
       </c>
+      <c r="N7" s="4"/>
+      <c r="O7" s="5">
+        <v>2</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.4303231921585335</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.4303231921585335</v>
+      </c>
+      <c r="R7" s="5">
+        <v>2</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3749,12 +4667,1686 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.4022496876642259</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.4022496876642259</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.4119442639276537</v>
+      </c>
+      <c r="E3" s="4">
+        <v>93.77551020408163</v>
+      </c>
+      <c r="F3" s="4">
+        <v>95.85570469798658</v>
+      </c>
+      <c r="G3" s="5">
+        <v>2</v>
+      </c>
+      <c r="H3" s="5">
+        <v>2</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4022496876642259</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.4022496876642259</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.2617371280431999</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.2617371280431999</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.2591037948370232</v>
+      </c>
+      <c r="E4" s="4">
+        <v>92.85714285714286</v>
+      </c>
+      <c r="F4" s="4">
+        <v>95.48657718120805</v>
+      </c>
+      <c r="G4" s="5">
+        <v>2</v>
+      </c>
+      <c r="H4" s="5">
+        <v>2</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>2</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2617371280431999</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2617371280431999</v>
+      </c>
+      <c r="R4" s="5">
+        <v>2</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.1509946110160987</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.1509946110160987</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.1737404587181535</v>
+      </c>
+      <c r="E5" s="4">
+        <v>93.5204081632653</v>
+      </c>
+      <c r="F5" s="4">
+        <v>95.85570469798658</v>
+      </c>
+      <c r="G5" s="5">
+        <v>2</v>
+      </c>
+      <c r="H5" s="5">
+        <v>2</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1509946110160987</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1509946110160987</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="4">
+        <v>0.03290313681934209</v>
+      </c>
+      <c r="C6" s="4">
+        <v>0.03290313681934209</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0.04563987454746099</v>
+      </c>
+      <c r="E6" s="4">
+        <v>88.46938775510205</v>
+      </c>
+      <c r="F6" s="4">
+        <v>94.68120805369128</v>
+      </c>
+      <c r="G6" s="5">
+        <v>2</v>
+      </c>
+      <c r="H6" s="5">
+        <v>2</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>0</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>2</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.03290313681934209</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.03290313681934209</v>
+      </c>
+      <c r="R6" s="5">
+        <v>2</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" s="4">
+        <v>0.06891427306252623</v>
+      </c>
+      <c r="C7" s="4">
+        <v>0.06891427306252623</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0.07145717112141753</v>
+      </c>
+      <c r="E7" s="4">
+        <v>88.36734693877551</v>
+      </c>
+      <c r="F7" s="4">
+        <v>94.37919463087249</v>
+      </c>
+      <c r="G7" s="5">
+        <v>2</v>
+      </c>
+      <c r="H7" s="5">
+        <v>2</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>0</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="4"/>
+      <c r="O7" s="5">
+        <v>2</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.06891427306252623</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.06891427306252623</v>
+      </c>
+      <c r="R7" s="5">
+        <v>2</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>1.297270172588372</v>
+      </c>
+      <c r="C3" s="4">
+        <v>1.297270172588372</v>
+      </c>
+      <c r="D3" s="4">
+        <v>1.375840300075554</v>
+      </c>
+      <c r="E3" s="4">
+        <v>84.74489795918367</v>
+      </c>
+      <c r="F3" s="4">
+        <v>86.34228187919463</v>
+      </c>
+      <c r="G3" s="5">
+        <v>2</v>
+      </c>
+      <c r="H3" s="5">
+        <v>2</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>1.297270172588372</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>1.297270172588372</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.7680056293248103</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.7680056293248103</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.8284495074986384</v>
+      </c>
+      <c r="E4" s="4">
+        <v>87.39795918367346</v>
+      </c>
+      <c r="F4" s="4">
+        <v>90.50335570469798</v>
+      </c>
+      <c r="G4" s="5">
+        <v>2</v>
+      </c>
+      <c r="H4" s="5">
+        <v>2</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>2</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.7680056293248103</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.7680056293248103</v>
+      </c>
+      <c r="R4" s="5">
+        <v>2</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.7590718986899069</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.7590718986899069</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.8197849514395407</v>
+      </c>
+      <c r="E5" s="4">
+        <v>90.66326530612245</v>
+      </c>
+      <c r="F5" s="4">
+        <v>93.57382550335571</v>
+      </c>
+      <c r="G5" s="5">
+        <v>2</v>
+      </c>
+      <c r="H5" s="5">
+        <v>2</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.7590718986899069</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.7590718986899069</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="4">
+        <v>0.6209464987215861</v>
+      </c>
+      <c r="C6" s="4">
+        <v>0.6209464987215861</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0.5764665623602733</v>
+      </c>
+      <c r="E6" s="4">
+        <v>84.84693877551021</v>
+      </c>
+      <c r="F6" s="4">
+        <v>91.77852348993288</v>
+      </c>
+      <c r="G6" s="5">
+        <v>2</v>
+      </c>
+      <c r="H6" s="5">
+        <v>2</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>0</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>2</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.6209464987215861</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.6209464987215861</v>
+      </c>
+      <c r="R6" s="5">
+        <v>2</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" s="4">
+        <v>0.3168147292526213</v>
+      </c>
+      <c r="C7" s="4">
+        <v>0.3168147292526213</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0.3119072702320351</v>
+      </c>
+      <c r="E7" s="4">
+        <v>85.30612244897959</v>
+      </c>
+      <c r="F7" s="4">
+        <v>91.61073825503355</v>
+      </c>
+      <c r="G7" s="5">
+        <v>2</v>
+      </c>
+      <c r="H7" s="5">
+        <v>2</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>0</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="4"/>
+      <c r="O7" s="5">
+        <v>2</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.3168147292526213</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.3168147292526213</v>
+      </c>
+      <c r="R7" s="5">
+        <v>2</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>100</v>
+      </c>
+      <c r="C3" s="3">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0.3618231758495004</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.3618231758495004</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0.3398022525963286</v>
+      </c>
+      <c r="K3" s="4">
+        <v>92.65306122448979</v>
+      </c>
+      <c r="L3" s="4">
+        <v>93.76398210290829</v>
+      </c>
+      <c r="M3" s="5">
+        <v>10</v>
+      </c>
+      <c r="N3" s="5">
+        <v>25182.52205848694</v>
+      </c>
+      <c r="O3" s="4">
+        <v>33.57669607798258</v>
+      </c>
+      <c r="P3" s="5">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>50</v>
+      </c>
+      <c r="C4" s="3">
+        <v>50</v>
+      </c>
+      <c r="D4" s="3">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.6901063054325937</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.817361300075975</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0.4865113347294687</v>
+      </c>
+      <c r="K4" s="4">
+        <v>75.5</v>
+      </c>
+      <c r="L4" s="4">
+        <v>70.99888143176734</v>
+      </c>
+      <c r="M4" s="5">
+        <v>10</v>
+      </c>
+      <c r="N4" s="5">
+        <v>76894.24228668213</v>
+      </c>
+      <c r="O4" s="4">
+        <v>53.10375848527772</v>
+      </c>
+      <c r="P4" s="5">
+        <v>1448</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>100</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.180871147741248</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.180871147741248</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0.1705064494951266</v>
+      </c>
+      <c r="K5" s="4">
+        <v>93.17602040816327</v>
+      </c>
+      <c r="L5" s="4">
+        <v>93.28020134228188</v>
+      </c>
+      <c r="M5" s="5">
+        <v>8</v>
+      </c>
+      <c r="N5" s="5">
+        <v>228729.3345928192</v>
+      </c>
+      <c r="O5" s="4">
+        <v>405.548465590105</v>
+      </c>
+      <c r="P5" s="5">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>70</v>
+      </c>
+      <c r="C6" s="3">
+        <v>30</v>
+      </c>
+      <c r="D6" s="3">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.1809374536201523</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.1385611752281373</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.1407584666904</v>
+      </c>
+      <c r="K6" s="4">
+        <v>83.69387755102041</v>
+      </c>
+      <c r="L6" s="4">
+        <v>82.70134228187919</v>
+      </c>
+      <c r="M6" s="5">
+        <v>10</v>
+      </c>
+      <c r="N6" s="5">
+        <v>105637.1743679047</v>
+      </c>
+      <c r="O6" s="4">
+        <v>90.83162026475034</v>
+      </c>
+      <c r="P6" s="5">
+        <v>1163</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>100</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.1966714733299711</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.1966714733299711</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0.199686896151016</v>
+      </c>
+      <c r="K7" s="4">
+        <v>93.40816326530613</v>
+      </c>
+      <c r="L7" s="4">
+        <v>95.11409395973155</v>
+      </c>
+      <c r="M7" s="5">
+        <v>10</v>
+      </c>
+      <c r="N7" s="5">
+        <v>109466.6414260864</v>
+      </c>
+      <c r="O7" s="4">
+        <v>163.6272667056598</v>
+      </c>
+      <c r="P7" s="5">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>90</v>
+      </c>
+      <c r="C8" s="3">
+        <v>10</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.3155747069462341</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.3338293848643101</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0.2859044500042818</v>
+      </c>
+      <c r="K8" s="4">
+        <v>91.24489795918367</v>
+      </c>
+      <c r="L8" s="4">
+        <v>89.39261744966443</v>
+      </c>
+      <c r="M8" s="5">
+        <v>10</v>
+      </c>
+      <c r="N8" s="5">
+        <v>10769.01793479919</v>
+      </c>
+      <c r="O8" s="4">
+        <v>12.95910702141901</v>
+      </c>
+      <c r="P8" s="5">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>60</v>
+      </c>
+      <c r="C9" s="3">
+        <v>40</v>
+      </c>
+      <c r="D9" s="3">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.3113517237934385</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.3291716776982386</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0.4365752173694883</v>
+      </c>
+      <c r="K9" s="4">
+        <v>72.87755102040816</v>
+      </c>
+      <c r="L9" s="4">
+        <v>72.55033557046978</v>
+      </c>
+      <c r="M9" s="5">
+        <v>10</v>
+      </c>
+      <c r="N9" s="5">
+        <v>52815.44327735901</v>
+      </c>
+      <c r="O9" s="4">
+        <v>31.34447672246825</v>
+      </c>
+      <c r="P9" s="5">
+        <v>1685</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>100</v>
+      </c>
+      <c r="C10" s="3">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.1538781511716635</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.1538781511716635</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.1634403641967807</v>
+      </c>
+      <c r="K10" s="4">
+        <v>84.91836734693878</v>
+      </c>
+      <c r="L10" s="4">
+        <v>90.73713646532437</v>
+      </c>
+      <c r="M10" s="5">
+        <v>10</v>
+      </c>
+      <c r="N10" s="5">
+        <v>67831.27784729004</v>
+      </c>
+      <c r="O10" s="4">
+        <v>89.36927252607384</v>
+      </c>
+      <c r="P10" s="5">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>60</v>
+      </c>
+      <c r="C11" s="3">
+        <v>40</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0.3047680800071015</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.3258221245395833</v>
+      </c>
+      <c r="J11" s="4">
+        <v>0.2109772876883408</v>
+      </c>
+      <c r="K11" s="4">
+        <v>82.94217687074831</v>
+      </c>
+      <c r="L11" s="4">
+        <v>80.04921700223714</v>
+      </c>
+      <c r="M11" s="5">
+        <v>10</v>
+      </c>
+      <c r="N11" s="5">
+        <v>53339.16974067688</v>
+      </c>
+      <c r="O11" s="4">
+        <v>41.73643954669552</v>
+      </c>
+      <c r="P11" s="5">
+        <v>1278</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>100</v>
+      </c>
+      <c r="C12" s="3">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.2010314553501963</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.2010314553501963</v>
+      </c>
+      <c r="J12" s="4">
+        <v>0.1911533053810605</v>
+      </c>
+      <c r="K12" s="4">
+        <v>89.20068027210885</v>
+      </c>
+      <c r="L12" s="4">
+        <v>90.92729306487698</v>
+      </c>
+      <c r="M12" s="5">
+        <v>10</v>
+      </c>
+      <c r="N12" s="5">
+        <v>17314.77618217468</v>
+      </c>
+      <c r="O12" s="4">
+        <v>20.27491356226544</v>
+      </c>
+      <c r="P12" s="5">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>90</v>
+      </c>
+      <c r="C13" s="3">
+        <v>10</v>
+      </c>
+      <c r="D13" s="3">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0.4990248292210459</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.4962024789587958</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0.4390067666294931</v>
+      </c>
+      <c r="K13" s="4">
+        <v>89.68367346938776</v>
+      </c>
+      <c r="L13" s="4">
+        <v>87.80536912751678</v>
+      </c>
+      <c r="M13" s="5">
+        <v>10</v>
+      </c>
+      <c r="N13" s="5">
+        <v>71083.80532264709</v>
+      </c>
+      <c r="O13" s="4">
+        <v>81.14589648704006</v>
+      </c>
+      <c r="P13" s="5">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3">
+        <v>100</v>
+      </c>
+      <c r="C14" s="3">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0.1755140472075467</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.1755140472075467</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0.1864784969124539</v>
+      </c>
+      <c r="K14" s="4">
+        <v>90.94897959183673</v>
+      </c>
+      <c r="L14" s="4">
+        <v>95.27852348993288</v>
+      </c>
+      <c r="M14" s="5">
+        <v>10</v>
+      </c>
+      <c r="N14" s="5">
+        <v>120506.8476200104</v>
+      </c>
+      <c r="O14" s="4">
+        <v>214.8072150089312</v>
+      </c>
+      <c r="P14" s="5">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3">
+        <v>100</v>
+      </c>
+      <c r="C15" s="3">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.5189965769174896</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.5189965769174896</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0.4905624538186166</v>
+      </c>
+      <c r="K15" s="4">
+        <v>85.76870748299319</v>
+      </c>
+      <c r="L15" s="4">
+        <v>90.36129753914987</v>
+      </c>
+      <c r="M15" s="5">
+        <v>10</v>
+      </c>
+      <c r="N15" s="5">
+        <v>184791.8872833252</v>
+      </c>
+      <c r="O15" s="4">
+        <v>218.4301268124411</v>
+      </c>
+      <c r="P15" s="5">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3">
+        <v>100</v>
+      </c>
+      <c r="C16" s="3">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>0</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.1833597673210786</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.1833597673210786</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0.1923771126303418</v>
+      </c>
+      <c r="K16" s="4">
+        <v>91.39795918367346</v>
+      </c>
+      <c r="L16" s="4">
+        <v>95.25167785234899</v>
+      </c>
+      <c r="M16" s="5">
+        <v>10</v>
+      </c>
+      <c r="N16" s="5">
+        <v>58469.17724609375</v>
+      </c>
+      <c r="O16" s="4">
+        <v>102.5775039405153</v>
+      </c>
+      <c r="P16" s="5">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="3">
+        <v>100</v>
+      </c>
+      <c r="C17" s="3">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0.7524217857154591</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0.7524217857154591</v>
+      </c>
+      <c r="J17" s="4">
+        <v>0.7824897183212083</v>
+      </c>
+      <c r="K17" s="4">
+        <v>86.59183673469387</v>
+      </c>
+      <c r="L17" s="4">
+        <v>90.76174496644295</v>
+      </c>
+      <c r="M17" s="5">
+        <v>10</v>
+      </c>
+      <c r="N17" s="5">
+        <v>73835.26062965393</v>
+      </c>
+      <c r="O17" s="4">
+        <v>100.0477786309674</v>
+      </c>
+      <c r="P17" s="5">
+        <v>738</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -4509,9 +7101,764 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:N17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>10</v>
+      </c>
+      <c r="C3" s="5">
+        <v>0</v>
+      </c>
+      <c r="D3" s="5">
+        <v>0</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0</v>
+      </c>
+      <c r="F3" s="5">
+        <v>0</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>5</v>
+      </c>
+      <c r="C4" s="5">
+        <v>5</v>
+      </c>
+      <c r="D4" s="5">
+        <v>0</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5">
+        <v>0</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>8</v>
+      </c>
+      <c r="C5" s="5">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5">
+        <v>0</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>7</v>
+      </c>
+      <c r="C6" s="5">
+        <v>3</v>
+      </c>
+      <c r="D6" s="5">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>0</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>10</v>
+      </c>
+      <c r="C7" s="5">
+        <v>0</v>
+      </c>
+      <c r="D7" s="5">
+        <v>0</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>0</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>1</v>
+      </c>
+      <c r="D8" s="5">
+        <v>0</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5">
+        <v>0</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>0</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>6</v>
+      </c>
+      <c r="C9" s="5">
+        <v>4</v>
+      </c>
+      <c r="D9" s="5">
+        <v>0</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0</v>
+      </c>
+      <c r="F9" s="5">
+        <v>0</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
+        <v>0</v>
+      </c>
+      <c r="I9" s="5">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>0</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5">
+        <v>10</v>
+      </c>
+      <c r="C10" s="5">
+        <v>0</v>
+      </c>
+      <c r="D10" s="5">
+        <v>0</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5">
+        <v>0</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <v>0</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>6</v>
+      </c>
+      <c r="C11" s="5">
+        <v>4</v>
+      </c>
+      <c r="D11" s="5">
+        <v>0</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5">
+        <v>0</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5">
+        <v>0</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>0</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>10</v>
+      </c>
+      <c r="C12" s="5">
+        <v>0</v>
+      </c>
+      <c r="D12" s="5">
+        <v>0</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5">
+        <v>0</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5">
+        <v>0</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>0</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5">
+        <v>9</v>
+      </c>
+      <c r="C13" s="5">
+        <v>1</v>
+      </c>
+      <c r="D13" s="5">
+        <v>0</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5">
+        <v>0</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5">
+        <v>0</v>
+      </c>
+      <c r="I13" s="5">
+        <v>0</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5">
+        <v>0</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5">
+        <v>10</v>
+      </c>
+      <c r="C14" s="5">
+        <v>0</v>
+      </c>
+      <c r="D14" s="5">
+        <v>0</v>
+      </c>
+      <c r="E14" s="5">
+        <v>0</v>
+      </c>
+      <c r="F14" s="5">
+        <v>0</v>
+      </c>
+      <c r="G14" s="5">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5">
+        <v>0</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5">
+        <v>0</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5">
+        <v>10</v>
+      </c>
+      <c r="C15" s="5">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5">
+        <v>0</v>
+      </c>
+      <c r="E15" s="5">
+        <v>0</v>
+      </c>
+      <c r="F15" s="5">
+        <v>0</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5">
+        <v>0</v>
+      </c>
+      <c r="I15" s="5">
+        <v>0</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5">
+        <v>0</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5">
+        <v>10</v>
+      </c>
+      <c r="C16" s="5">
+        <v>0</v>
+      </c>
+      <c r="D16" s="5">
+        <v>0</v>
+      </c>
+      <c r="E16" s="5">
+        <v>0</v>
+      </c>
+      <c r="F16" s="5">
+        <v>0</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5">
+        <v>0</v>
+      </c>
+      <c r="I16" s="5">
+        <v>0</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <v>0</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="5">
+        <v>10</v>
+      </c>
+      <c r="C17" s="5">
+        <v>0</v>
+      </c>
+      <c r="D17" s="5">
+        <v>0</v>
+      </c>
+      <c r="E17" s="5">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5">
+        <v>0</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5">
+        <v>0</v>
+      </c>
+      <c r="I17" s="5">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <v>0</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4522,9 +7869,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4558,8 +7911,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4581,25 +7942,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2930241909416308</v>
+        <v>0.09163134250421873</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2930241909416308</v>
+        <v>0.09163134250421873</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3026830044181933</v>
+        <v>0.05418145035945315</v>
       </c>
       <c r="E3" s="4">
-        <v>94.28571428571429</v>
+        <v>86.12244897959184</v>
       </c>
       <c r="F3" s="4">
-        <v>96.90156599552573</v>
+        <v>85.30201342281879</v>
       </c>
       <c r="G3" s="5">
         <v>2</v>
@@ -4622,10 +8001,26 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.09163134250421873</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.09163134250421873</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.5907952587366563</v>
@@ -4663,25 +8058,41 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>2</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.5907952587366563</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.5907952587366563</v>
+      </c>
+      <c r="R4" s="5">
+        <v>2</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.09163134250421873</v>
+        <v>0.1042702915580625</v>
       </c>
       <c r="C5" s="4">
-        <v>0.09163134250421873</v>
+        <v>0.1042702915580625</v>
       </c>
       <c r="D5" s="4">
-        <v>0.05418145035945315</v>
+        <v>0.1093095066459531</v>
       </c>
       <c r="E5" s="4">
-        <v>86.12244897959184</v>
+        <v>96.68367346938776</v>
       </c>
       <c r="F5" s="4">
-        <v>85.30201342281879</v>
+        <v>97.3993288590604</v>
       </c>
       <c r="G5" s="5">
         <v>2</v>
@@ -4704,10 +8115,26 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1042702915580625</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1042702915580625</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
         <v>0.7293947955069336</v>
@@ -4745,25 +8172,41 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>2</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.7293947955069336</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.7293947955069336</v>
+      </c>
+      <c r="R6" s="5">
+        <v>2</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B7" s="4">
-        <v>0.1042702915580625</v>
+        <v>0.2930241909416308</v>
       </c>
       <c r="C7" s="4">
-        <v>0.1042702915580625</v>
+        <v>0.2930241909416308</v>
       </c>
       <c r="D7" s="4">
-        <v>0.1093095066459531</v>
+        <v>0.3026830044181933</v>
       </c>
       <c r="E7" s="4">
-        <v>96.68367346938776</v>
+        <v>94.28571428571429</v>
       </c>
       <c r="F7" s="4">
-        <v>97.3993288590604</v>
+        <v>96.90156599552573</v>
       </c>
       <c r="G7" s="5">
         <v>2</v>
@@ -4786,9 +8229,25 @@
       <c r="M7" s="5">
         <v>0</v>
       </c>
+      <c r="N7" s="4"/>
+      <c r="O7" s="5">
+        <v>2</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.2930241909416308</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.2930241909416308</v>
+      </c>
+      <c r="R7" s="5">
+        <v>2</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4799,14 +8258,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4817,9 +8277,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4853,8 +8319,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4876,34 +8350,50 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.5368086185844531</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.5368086185844531</v>
-      </c>
+        <v>0.3561006846503125</v>
+      </c>
+      <c r="C3" s="4"/>
       <c r="D3" s="4">
-        <v>0.4929548588188281</v>
+        <v>0.08048880720890622</v>
       </c>
       <c r="E3" s="4">
-        <v>86.64965986394557</v>
+        <v>60.08503401360544</v>
       </c>
       <c r="F3" s="4">
-        <v>88.93736017897091</v>
+        <v>49.26174496644295</v>
       </c>
       <c r="G3" s="5">
         <v>2</v>
       </c>
       <c r="H3" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3" s="5">
         <v>0</v>
@@ -4917,10 +8407,24 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3561006846503125</v>
+      </c>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="5">
+        <v>0</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.9850213329554063</v>
@@ -4958,25 +8462,39 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.9850213329554063</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>1.069084349321125</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.3561006846503125</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0</v>
-      </c>
+        <v>0.6005484340278749</v>
+      </c>
+      <c r="C5" s="4"/>
       <c r="D5" s="4">
-        <v>0.08048880720890622</v>
+        <v>0.2141196010200625</v>
       </c>
       <c r="E5" s="4">
-        <v>60.08503401360544</v>
+        <v>63.11224489795919</v>
       </c>
       <c r="F5" s="4">
-        <v>49.26174496644295</v>
+        <v>49.21140939597316</v>
       </c>
       <c r="G5" s="5">
         <v>2</v>
@@ -4999,10 +8517,24 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>0</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.6005484340278749</v>
+      </c>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="5">
+        <v>0</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
         <v>0.9720524569449219</v>
@@ -5040,34 +8572,50 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>2</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.9720524569449219</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.9720524569449219</v>
+      </c>
+      <c r="R6" s="5">
+        <v>2</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B7" s="4">
-        <v>0.6005484340278749</v>
+        <v>0.5368086185844531</v>
       </c>
       <c r="C7" s="4">
-        <v>0</v>
+        <v>0.5368086185844531</v>
       </c>
       <c r="D7" s="4">
-        <v>0.2141196010200625</v>
+        <v>0.4929548588188281</v>
       </c>
       <c r="E7" s="4">
-        <v>63.11224489795919</v>
+        <v>86.64965986394557</v>
       </c>
       <c r="F7" s="4">
-        <v>49.21140939597316</v>
+        <v>88.93736017897091</v>
       </c>
       <c r="G7" s="5">
         <v>2</v>
       </c>
       <c r="H7" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J7" s="5">
         <v>0</v>
@@ -5081,9 +8629,25 @@
       <c r="M7" s="5">
         <v>0</v>
       </c>
+      <c r="N7" s="4"/>
+      <c r="O7" s="5">
+        <v>2</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.5368086185844531</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.5368086185844531</v>
+      </c>
+      <c r="R7" s="5">
+        <v>2</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -5094,14 +8658,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -5112,9 +8677,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -5148,8 +8719,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -5171,31 +8750,49 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2764777201085205</v>
+        <v>0.0551007476969852</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2764777201085205</v>
+        <v>0.0551007476969852</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2679037111668701</v>
+        <v>0.09711137538396258</v>
       </c>
       <c r="E3" s="4">
-        <v>95.91836734693878</v>
+        <v>88.57142857142857</v>
       </c>
       <c r="F3" s="4">
-        <v>97.71812080536913</v>
+        <v>86.97986577181209</v>
       </c>
       <c r="G3" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
@@ -5212,10 +8809,26 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.0551007476969852</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.0551007476969852</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.3448392997742158</v>
@@ -5253,25 +8866,41 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>2</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3448392997742158</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.3448392997742158</v>
+      </c>
+      <c r="R4" s="5">
+        <v>2</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.0551007476969852</v>
+        <v>0.04704001075907998</v>
       </c>
       <c r="C5" s="4">
-        <v>0.0551007476969852</v>
+        <v>0.04704001075907998</v>
       </c>
       <c r="D5" s="4">
-        <v>0.09711137538396258</v>
+        <v>0.03506571329518609</v>
       </c>
       <c r="E5" s="4">
-        <v>88.57142857142857</v>
+        <v>96.22448979591837</v>
       </c>
       <c r="F5" s="4">
-        <v>86.97986577181209</v>
+        <v>96.66107382550335</v>
       </c>
       <c r="G5" s="5">
         <v>2</v>
@@ -5294,10 +8923,26 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.04704001075907998</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.04704001075907998</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
         <v>0.2765313453609013</v>
@@ -5335,31 +8980,47 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>1</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.2765313453609013</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.2765313453609013</v>
+      </c>
+      <c r="R6" s="5">
+        <v>1</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B7" s="4">
-        <v>0.04704001075907998</v>
+        <v>0.2764777201085205</v>
       </c>
       <c r="C7" s="4">
-        <v>0.04704001075907998</v>
+        <v>0.2764777201085205</v>
       </c>
       <c r="D7" s="4">
-        <v>0.03506571329518609</v>
+        <v>0.2679037111668701</v>
       </c>
       <c r="E7" s="4">
-        <v>96.22448979591837</v>
+        <v>95.91836734693878</v>
       </c>
       <c r="F7" s="4">
-        <v>96.66107382550335</v>
+        <v>97.71812080536913</v>
       </c>
       <c r="G7" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H7" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I7" s="5">
         <v>0</v>
@@ -5376,9 +9037,25 @@
       <c r="M7" s="5">
         <v>0</v>
       </c>
+      <c r="N7" s="4"/>
+      <c r="O7" s="5">
+        <v>1</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.2764777201085205</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.2764777201085205</v>
+      </c>
+      <c r="R7" s="5">
+        <v>1</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -5389,14 +9066,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -5407,9 +9085,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -5443,8 +9127,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -5466,34 +9158,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3106018391044726</v>
+        <v>0.05538689469539065</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3106018391044726</v>
+        <v>0.08085912885132818</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2825094547660937</v>
+        <v>0.1138814625664844</v>
       </c>
       <c r="E3" s="4">
-        <v>89.13265306122449</v>
+        <v>84.26870748299319</v>
       </c>
       <c r="F3" s="4">
-        <v>92.26510067114094</v>
+        <v>82.85234899328859</v>
       </c>
       <c r="G3" s="5">
         <v>2</v>
       </c>
       <c r="H3" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="5">
         <v>0</v>
@@ -5507,17 +9217,31 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.05538689469539065</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.08085912885132818</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.4047658245325547</v>
       </c>
-      <c r="C4" s="4">
-        <v>0</v>
-      </c>
+      <c r="C4" s="4"/>
       <c r="D4" s="4">
         <v>0.1695044238805312</v>
       </c>
@@ -5548,34 +9272,48 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>0</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4047658245325547</v>
+      </c>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="5">
+        <v>0</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.05538689469539065</v>
+        <v>0.0139997704538125</v>
       </c>
       <c r="C5" s="4">
-        <v>0.08085912885132818</v>
+        <v>0.0139997704538125</v>
       </c>
       <c r="D5" s="4">
-        <v>0.1138814625664844</v>
+        <v>0.01673953510209374</v>
       </c>
       <c r="E5" s="4">
-        <v>84.26870748299319</v>
+        <v>91.07142857142857</v>
       </c>
       <c r="F5" s="4">
-        <v>82.85234899328859</v>
+        <v>95.40268456375838</v>
       </c>
       <c r="G5" s="5">
         <v>2</v>
       </c>
       <c r="H5" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" s="5">
         <v>0</v>
@@ -5589,10 +9327,26 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.0139997704538125</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.0139997704538125</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
         <v>0.1199329393145313</v>
@@ -5630,25 +9384,41 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>2</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.1199329393145313</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.1199329393145313</v>
+      </c>
+      <c r="R6" s="5">
+        <v>2</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B7" s="4">
-        <v>0.0139997704538125</v>
+        <v>0.3106018391044726</v>
       </c>
       <c r="C7" s="4">
-        <v>0.0139997704538125</v>
+        <v>0.3106018391044726</v>
       </c>
       <c r="D7" s="4">
-        <v>0.01673953510209374</v>
+        <v>0.2825094547660937</v>
       </c>
       <c r="E7" s="4">
-        <v>91.07142857142857</v>
+        <v>89.13265306122449</v>
       </c>
       <c r="F7" s="4">
-        <v>95.40268456375838</v>
+        <v>92.26510067114094</v>
       </c>
       <c r="G7" s="5">
         <v>2</v>
@@ -5671,9 +9441,25 @@
       <c r="M7" s="5">
         <v>0</v>
       </c>
+      <c r="N7" s="4"/>
+      <c r="O7" s="5">
+        <v>2</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.3106018391044726</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.3106018391044726</v>
+      </c>
+      <c r="R7" s="5">
+        <v>2</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -5684,14 +9470,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -5702,9 +9489,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -5738,8 +9531,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -5761,25 +9562,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.225301393547832</v>
+        <v>0.10961281632625</v>
       </c>
       <c r="C3" s="4">
-        <v>0.225301393547832</v>
+        <v>0.10961281632625</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2229405727775683</v>
+        <v>0.1420873341485157</v>
       </c>
       <c r="E3" s="4">
-        <v>92.34693877551021</v>
+        <v>91.88775510204081</v>
       </c>
       <c r="F3" s="4">
-        <v>96.00671140939598</v>
+        <v>91.92953020134229</v>
       </c>
       <c r="G3" s="5">
         <v>2</v>
@@ -5802,10 +9621,26 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.10961281632625</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.10961281632625</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.2400910656214219</v>
@@ -5843,25 +9678,41 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>2</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2400910656214219</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2400910656214219</v>
+      </c>
+      <c r="R4" s="5">
+        <v>2</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.10961281632625</v>
+        <v>0.1272900822074766</v>
       </c>
       <c r="C5" s="4">
-        <v>0.10961281632625</v>
+        <v>0.1272900822074766</v>
       </c>
       <c r="D5" s="4">
-        <v>0.1420873341485157</v>
+        <v>0.1409924747856016</v>
       </c>
       <c r="E5" s="4">
-        <v>91.88775510204081</v>
+        <v>96.68367346938776</v>
       </c>
       <c r="F5" s="4">
-        <v>91.92953020134229</v>
+        <v>97.29865771812081</v>
       </c>
       <c r="G5" s="5">
         <v>2</v>
@@ -5884,10 +9735,26 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1272900822074766</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1272900822074766</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
         <v>0.2810620089468751</v>
@@ -5925,25 +9792,41 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>2</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.2810620089468751</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.2810620089468751</v>
+      </c>
+      <c r="R6" s="5">
+        <v>2</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B7" s="4">
-        <v>0.1272900822074766</v>
+        <v>0.225301393547832</v>
       </c>
       <c r="C7" s="4">
-        <v>0.1272900822074766</v>
+        <v>0.225301393547832</v>
       </c>
       <c r="D7" s="4">
-        <v>0.1409924747856016</v>
+        <v>0.2229405727775683</v>
       </c>
       <c r="E7" s="4">
-        <v>96.68367346938776</v>
+        <v>92.34693877551021</v>
       </c>
       <c r="F7" s="4">
-        <v>97.29865771812081</v>
+        <v>96.00671140939598</v>
       </c>
       <c r="G7" s="5">
         <v>2</v>
@@ -5966,9 +9849,25 @@
       <c r="M7" s="5">
         <v>0</v>
       </c>
+      <c r="N7" s="4"/>
+      <c r="O7" s="5">
+        <v>2</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.225301393547832</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.225301393547832</v>
+      </c>
+      <c r="R7" s="5">
+        <v>2</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -5979,596 +9878,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.1901778159201312</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.1901778159201312</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.1927947598954431</v>
-      </c>
-      <c r="E3" s="4">
-        <v>93.82653061224489</v>
-      </c>
-      <c r="F3" s="4">
-        <v>96.30872483221476</v>
-      </c>
-      <c r="G3" s="5">
-        <v>2</v>
-      </c>
-      <c r="H3" s="5">
-        <v>2</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.5063011415515828</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.5063011415515828</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.4336391435909601</v>
-      </c>
-      <c r="E4" s="4">
-        <v>88.5204081632653</v>
-      </c>
-      <c r="F4" s="4">
-        <v>82.78523489932886</v>
-      </c>
-      <c r="G4" s="5">
-        <v>2</v>
-      </c>
-      <c r="H4" s="5">
-        <v>2</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.0989705466116288</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.04665848753970803</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.06890249147884159</v>
-      </c>
-      <c r="E5" s="4">
-        <v>87.95918367346938</v>
-      </c>
-      <c r="F5" s="4">
-        <v>82.34899328859061</v>
-      </c>
-      <c r="G5" s="5">
-        <v>2</v>
-      </c>
-      <c r="H5" s="5">
-        <v>1</v>
-      </c>
-      <c r="I5" s="5">
-        <v>1</v>
-      </c>
-      <c r="J5" s="5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B6" s="4">
-        <v>0.5791185515845066</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0.5791185515845066</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0.5680738591443836</v>
-      </c>
-      <c r="E6" s="4">
-        <v>93.21428571428571</v>
-      </c>
-      <c r="F6" s="4">
-        <v>95.85570469798658</v>
-      </c>
-      <c r="G6" s="5">
-        <v>2</v>
-      </c>
-      <c r="H6" s="5">
-        <v>2</v>
-      </c>
-      <c r="I6" s="5">
-        <v>0</v>
-      </c>
-      <c r="J6" s="5">
-        <v>0</v>
-      </c>
-      <c r="K6" s="5">
-        <v>0</v>
-      </c>
-      <c r="L6" s="5">
-        <v>0</v>
-      </c>
-      <c r="M6" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
-      <c r="A7" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B7" s="4">
-        <v>0.203305479063321</v>
-      </c>
-      <c r="C7" s="4">
-        <v>0.203305479063321</v>
-      </c>
-      <c r="D7" s="4">
-        <v>0.1661119959117807</v>
-      </c>
-      <c r="E7" s="4">
-        <v>92.70408163265306</v>
-      </c>
-      <c r="F7" s="4">
-        <v>89.66442953020135</v>
-      </c>
-      <c r="G7" s="5">
-        <v>2</v>
-      </c>
-      <c r="H7" s="5">
-        <v>2</v>
-      </c>
-      <c r="I7" s="5">
-        <v>0</v>
-      </c>
-      <c r="J7" s="5">
-        <v>0</v>
-      </c>
-      <c r="K7" s="5">
-        <v>0</v>
-      </c>
-      <c r="L7" s="5">
-        <v>0</v>
-      </c>
-      <c r="M7" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.1790675011070361</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.1790675011070361</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.1656404819877734</v>
-      </c>
-      <c r="E3" s="4">
-        <v>79.03061224489795</v>
-      </c>
-      <c r="F3" s="4">
-        <v>86.19127516778524</v>
-      </c>
-      <c r="G3" s="5">
-        <v>2</v>
-      </c>
-      <c r="H3" s="5">
-        <v>2</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.2162878711461562</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.2285078137648125</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.5200903613805312</v>
-      </c>
-      <c r="E4" s="4">
-        <v>70.56122448979592</v>
-      </c>
-      <c r="F4" s="4">
-        <v>65.1062639821029</v>
-      </c>
-      <c r="G4" s="5">
-        <v>2</v>
-      </c>
-      <c r="H4" s="5">
-        <v>1</v>
-      </c>
-      <c r="I4" s="5">
-        <v>1</v>
-      </c>
-      <c r="J4" s="5">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.7018941578789843</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.8112256956957031</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.8906415638848437</v>
-      </c>
-      <c r="E5" s="4">
-        <v>68.46938775510205</v>
-      </c>
-      <c r="F5" s="4">
-        <v>68.47315436241611</v>
-      </c>
-      <c r="G5" s="5">
-        <v>2</v>
-      </c>
-      <c r="H5" s="5">
-        <v>1</v>
-      </c>
-      <c r="I5" s="5">
-        <v>1</v>
-      </c>
-      <c r="J5" s="5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B6" s="4">
-        <v>0.2885807772574219</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0.2885807772574219</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0.3125265856680665</v>
-      </c>
-      <c r="E6" s="4">
-        <v>79.64285714285714</v>
-      </c>
-      <c r="F6" s="4">
-        <v>87.85234899328859</v>
-      </c>
-      <c r="G6" s="5">
-        <v>2</v>
-      </c>
-      <c r="H6" s="5">
-        <v>2</v>
-      </c>
-      <c r="I6" s="5">
-        <v>0</v>
-      </c>
-      <c r="J6" s="5">
-        <v>0</v>
-      </c>
-      <c r="K6" s="5">
-        <v>0</v>
-      </c>
-      <c r="L6" s="5">
-        <v>0</v>
-      </c>
-      <c r="M6" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
-      <c r="A7" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B7" s="4">
-        <v>0.1709283115775938</v>
-      </c>
-      <c r="C7" s="4">
-        <v>0</v>
-      </c>
-      <c r="D7" s="4">
-        <v>0.2939770939262266</v>
-      </c>
-      <c r="E7" s="4">
-        <v>66.68367346938776</v>
-      </c>
-      <c r="F7" s="4">
-        <v>55.12863534675616</v>
-      </c>
-      <c r="G7" s="5">
-        <v>2</v>
-      </c>
-      <c r="H7" s="5">
-        <v>0</v>
-      </c>
-      <c r="I7" s="5">
-        <v>2</v>
-      </c>
-      <c r="J7" s="5">
-        <v>0</v>
-      </c>
-      <c r="K7" s="5">
-        <v>0</v>
-      </c>
-      <c r="L7" s="5">
-        <v>0</v>
-      </c>
-      <c r="M7" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
